--- a/monchef-cafe/ttk/out/Реестр ТТК и СТО.xlsx
+++ b/monchef-cafe/ttk/out/Реестр ТТК и СТО.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр ТТК'!$A$1:$N$235</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Папки и СТО'!$A$1:$I$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Отклонения'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Отклонения'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -706,7 +706,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>дописать в п. 5 карты: блюдо собирают по заказу и реализуют сразу; покупные компоненты хранят по условиям изготовителя, собственные п/ф — по СТО их папок</t>
+          <t>п. 5 карты: блюдо готовят по заказу и реализуют сразу; заготовки — отдельными картами п/ф по СТО их папок (02.xx), покупные компоненты — по условиям изготовителя</t>
         </is>
       </c>
     </row>
@@ -1629,9 +1629,7 @@
           <t>5.1. Шницель нарезают на 8 частей, выкладывают с картофелем фри, поливают соусом, украшают зеленью и малосольными огурцами. Температура подачи — не ниже +65 °С. 5.2. Блюдо готовят по заказу и реализуют сразу после приготовления; хранение не допускается.</t>
         </is>
       </c>
-      <c r="K20" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -2511,64 +2509,70 @@
       <c r="N35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Борщ с говядиной</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Раздел 3. Супы</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>01.08 Супы</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>ТТК кафе/01 Блюда/01.08 Супы</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>СТО 01.08-2026</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>A — Блюдо</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>сразу</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>5.1. Борщ перекладывают в посуду для подачи, посыпают зеленью. Сметану подают в соуснике, ржаную булочку — прогретой. Температура подачи — не ниже +75 °С. Вариант для деловых обедов (по ТИ): вместо томлёной говядины — куриное филе отварное 40 г, остальное без изменений. Заготовка борща: при −12 °С — 30 суток (по ТИ; рекомендуется −18 °С), при +2…+6 °С — 7 суток. 5.2. Блюдо готовят по заказу и реализуют сразу после приготовления; хранение не допускается.</t>
         </is>
       </c>
-      <c r="K36" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>соответствует</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+      <c r="K36" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>в карте блюда указано хранение заготовки (охл. 7 сут; зам. 30 сут) — заготовку оформить отдельной картой полуфабриката в папке 02 и хранить по её СТО</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>п. 5 карты: блюдо готовят по заказу и реализуют сразу; заготовки — отдельными картами п/ф по СТО их папок (02.xx), покупные компоненты — по условиям изготовителя</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -9865,9 +9869,7 @@
           <t>5.1. Нарезают на 6 частей. Температура подачи — не ниже +65 °С. 5.2. Блюдо готовят по заказу и реализуют сразу после приготовления; хранение не допускается.</t>
         </is>
       </c>
-      <c r="K159" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr"/>
       <c r="M159" s="2" t="inlineStr">
         <is>
@@ -9925,9 +9927,7 @@
           <t>5.1. Нарезают на 6 частей. Температура подачи — не ниже +65 °С. 5.2. Блюдо готовят по заказу и реализуют сразу после приготовления; хранение не допускается.</t>
         </is>
       </c>
-      <c r="K160" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr"/>
       <c r="M160" s="2" t="inlineStr">
         <is>
@@ -9985,9 +9985,7 @@
           <t>5.1. Нарезают на 6 частей. Температура подачи — не ниже +65 °С. 5.2. Блюдо готовят по заказу и реализуют сразу после приготовления; хранение не допускается.</t>
         </is>
       </c>
-      <c r="K161" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr"/>
       <c r="M161" s="2" t="inlineStr">
         <is>
@@ -14880,7 +14878,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -15642,7 +15640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -15711,62 +15709,62 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>дописать в п. 5 карты: блюдо собирают по заказу и реализуют сразу; покупные компоненты хранят по условиям изготовителя, собственные п/ф — по СТО их папок</t>
+          <t>п. 5 карты: блюдо готовят по заказу и реализуют сразу; заготовки — отдельными картами п/ф по СТО их папок (02.xx), покупные компоненты — по условиям изготовителя</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Сырники (полуфабрикат)</t>
+          <t>Борщ с говядиной</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>02.13</t>
+          <t>01.08</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Охлаждённые: при +2…+4 °С не более 72 ч (по ТИ — 3 суток). Замороженные: при −18 °С, срок устанавливается изготовителем.</t>
+          <t>5.1. Борщ перекладывают в посуду для подачи, посыпают зеленью. Сметану подают в соуснике, ржаную булочку — прогретой. Температура подачи — не ниже +75 °С. Вариант для деловых обедов (по ТИ): вместо томлёной говядины — куриное филе отварное 40 г, остальное без изменений. Заготовка борща: при −12 °С — 30 суток (по ТИ; рекомендуется −18 °С), при +2…+6 °С — 7 суток. 5.2. Блюдо готовят по заказу и реализуют сразу после приготовления; хранение не допускается.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>срок охлаждённого 72 ч больше нормы СТО 24 ч</t>
+          <t>в карте блюда указано хранение заготовки (охл. 7 сут; зам. 30 сут) — заготовку оформить отдельной картой полуфабриката в папке 02 и хранить по её СТО</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>привести срок в карте к норме СТО либо обосновать больший срок лабораторными исследованиями (МУК 4.2.1847-04) и внести изменение в СТО</t>
+          <t>п. 5 карты: блюдо готовят по заказу и реализуют сразу; заготовки — отдельными картами п/ф по СТО их папок (02.xx), покупные компоненты — по условиям изготовителя</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Лосось слабосолёный (полуфабрикат)</t>
+          <t>Сырники (полуфабрикат)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>02.06</t>
+          <t>02.13</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>При −18 °С — не более 60 суток; в вакууме при +2…+3 °С — не более 5 суток.</t>
+          <t>Охлаждённые: при +2…+4 °С не более 72 ч (по ТИ — 3 суток). Замороженные: при −18 °С, срок устанавливается изготовителем.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>срок охлаждённого 5 сут больше нормы СТО 48 ч; срок замороженного 60 сут больше нормы СТО 30 сут</t>
+          <t>срок охлаждённого 72 ч больше нормы СТО 24 ч</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -15777,26 +15775,26 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Соус «Спайси» (полуфабрикат)</t>
+          <t>Лосось слабосолёный (полуфабрикат)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>02.02</t>
+          <t>02.06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Хранить в вакууме при +2…+6 °С не более 14 суток (по ТИ). Срок подлежит подтверждению лабораторными исследованиями.</t>
+          <t>При −18 °С — не более 60 суток; в вакууме при +2…+3 °С — не более 5 суток.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>срок охлаждённого 14 сут больше нормы СТО 72 ч</t>
+          <t>срок охлаждённого 5 сут больше нормы СТО 48 ч; срок замороженного 60 сут больше нормы СТО 30 сут</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -15807,26 +15805,26 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Говядина томлёная (полуфабрикат)</t>
+          <t>Соус «Спайси» (полуфабрикат)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>02.04</t>
+          <t>02.02</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Хранить в вакууме при +2…+6 °С не более 5 суток либо при −18 °С не более 30 суток.</t>
+          <t>Хранить в вакууме при +2…+6 °С не более 14 суток (по ТИ). Срок подлежит подтверждению лабораторными исследованиями.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>срок охлаждённого 5 сут больше нормы СТО 72 ч</t>
+          <t>срок охлаждённого 14 сут больше нормы СТО 72 ч</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -15837,26 +15835,26 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Соус «Цезарь» (полуфабрикат)</t>
+          <t>Говядина томлёная (полуфабрикат)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>02.02</t>
+          <t>02.04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Хранить в вакууме при +2…+6 °С не более 14 суток (по ТИ). Срок подлежит подтверждению лабораторными исследованиями.</t>
+          <t>Хранить в вакууме при +2…+6 °С не более 5 суток либо при −18 °С не более 30 суток.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>срок охлаждённого 14 сут больше нормы СТО 72 ч</t>
+          <t>срок охлаждённого 5 сут больше нормы СТО 72 ч</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -15867,26 +15865,26 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Соус кунжутный чили (полуфабрикат)</t>
+          <t>Соус «Цезарь» (полуфабрикат)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>02.03</t>
+          <t>02.02</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Хранить при +2…+6 °С не более 14 суток.</t>
+          <t>Хранить в вакууме при +2…+6 °С не более 14 суток (по ТИ). Срок подлежит подтверждению лабораторными исследованиями.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>срок охлаждённого 14 сут больше нормы СТО 7 сут</t>
+          <t>срок охлаждённого 14 сут больше нормы СТО 72 ч</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -15897,26 +15895,26 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Пастрами из говядины (полуфабрикат)</t>
+          <t>Соус кунжутный чили (полуфабрикат)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>02.04</t>
+          <t>02.03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Хранить в вакууме при +2…+6 °С не более 7 суток либо при −18 °С не более 60 суток.</t>
+          <t>Хранить при +2…+6 °С не более 14 суток.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>срок охлаждённого 7 сут больше нормы СТО 72 ч; срок замороженного 60 сут больше нормы СТО 30 сут</t>
+          <t>срок охлаждённого 14 сут больше нормы СТО 7 сут</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -15927,11 +15925,11 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Пастрами из индейки (полуфабрикат)</t>
+          <t>Пастрами из говядины (полуфабрикат)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -15941,12 +15939,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Хранить в вакууме при +2…+4 °С не более 5 суток.</t>
+          <t>Хранить в вакууме при +2…+6 °С не более 7 суток либо при −18 °С не более 60 суток.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>срок охлаждённого 5 сут больше нормы СТО 72 ч</t>
+          <t>срок охлаждённого 7 сут больше нормы СТО 72 ч; срок замороженного 60 сут больше нормы СТО 30 сут</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -15957,11 +15955,11 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Бедро куриное су-вид (полуфабрикат)</t>
+          <t>Пастрами из индейки (полуфабрикат)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -15987,11 +15985,11 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>169</v>
+        <v>70</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Куриная грудка су-вид</t>
+          <t>Бедро куриное су-вид (полуфабрикат)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -16017,11 +16015,11 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Щёчки телячьи томлёные</t>
+          <t>Куриная грудка су-вид</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -16031,7 +16029,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Хранить в вакууме при +2…+6 °С не более 5 суток; при −18 °С не более 30 суток.</t>
+          <t>Хранить в вакууме при +2…+4 °С не более 5 суток.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -16047,26 +16045,26 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Сырная шапка</t>
+          <t>Щёчки телячьи томлёные</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>02.13</t>
+          <t>02.04</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Хранить при +2…+6 °С не более 24 ч.</t>
+          <t>Хранить в вакууме при +2…+6 °С не более 5 суток; при −18 °С не более 30 суток.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>срок охлаждённого 24 ч больше нормы СТО 6 ч</t>
+          <t>срок охлаждённого 5 сут больше нормы СТО 72 ч</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -16077,41 +16075,41 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Салат «Оливье» (на 10 порций)</t>
+          <t>Сырная шапка</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>02.09</t>
+          <t>02.13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Без заправки — при +2…+4 °С не более 12 ч; заправленный — не более 6 ч (СанПиН 2.3/2.4.3590-20).</t>
+          <t>Хранить при +2…+6 °С не более 24 ч.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>хранение заправленного салата 6 ч — по СТО салат заправляют перед подачей</t>
+          <t>срок охлаждённого 24 ч больше нормы СТО 6 ч</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>исправить п. 5 карты: заправлять перед подачей, хранить только незаправленную заготовку</t>
+          <t>привести срок в карте к норме СТО либо обосновать больший срок лабораторными исследованиями (МУК 4.2.1847-04) и внести изменение в СТО</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Салат с говяжьей печенью (на 10 порций)</t>
+          <t>Салат «Оливье» (на 10 порций)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -16121,7 +16119,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Без заправки — при +2…+4 °С не более 12 ч; заправленный — не более 6 ч.</t>
+          <t>Без заправки — при +2…+4 °С не более 12 ч; заправленный — не более 6 ч (СанПиН 2.3/2.4.3590-20).</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -16137,11 +16135,11 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Салат «Соблазн» (на 10 порций)</t>
+          <t>Салат с говяжьей печенью (на 10 порций)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -16167,36 +16165,66 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Салат «Соблазн» (на 10 порций)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>02.09</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Без заправки — при +2…+4 °С не более 12 ч; заправленный — не более 6 ч.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>хранение заправленного салата 6 ч — по СТО салат заправляют перед подачей</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>исправить п. 5 карты: заправлять перед подачей, хранить только незаправленную заготовку</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
         <v>218</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Куриное филе копчёное</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>02.04</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Хранить в вакууме при +2…+4 °С не более 5 суток.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>срок охлаждённого 5 сут больше нормы СТО 72 ч</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>привести срок в карте к норме СТО либо обосновать больший срок лабораторными исследованиями (МУК 4.2.1847-04) и внести изменение в СТО</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F18"/>
+  <autoFilter ref="A1:F19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/monchef-cafe/ttk/out/Реестр ТТК и СТО.xlsx
+++ b/monchef-cafe/ttk/out/Реестр ТТК и СТО.xlsx
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Салат «Греческий</t>
+          <t>Салат «Греческий»</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Десерт «Бутерброд с икрой</t>
+          <t>Десерт «Бутерброд с икрой»</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Десерт «Яйцо всмятку</t>
+          <t>Десерт «Яйцо всмятку»</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Пирожное «Картошка</t>
+          <t>Пирожное «Картошка»</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Пирожное «Наполеон</t>
+          <t>Пирожное «Наполеон»</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Филе дорадо в соусе «Том Ям</t>
+          <t>Филе дорадо в соусе «Том Ям»</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Куриный супчик «Алфавит</t>
+          <t>Куриный супчик «Алфавит»</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Детский бургер «Для богатырей</t>
+          <t>Детский бургер «Для богатырей»</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Детский бургер «Та самая Ряба</t>
+          <t>Детский бургер «Та самая Ряба»</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Ролл «Филадельфия</t>
+          <t>Ролл «Филадельфия»</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Ролл «Филадельфия лайт</t>
+          <t>Ролл «Филадельфия лайт»</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Ролл «Калифорния</t>
+          <t>Ролл «Калифорния»</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Ролл «Бонито</t>
+          <t>Ролл «Бонито»</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Ролл «Чикен</t>
+          <t>Ролл «Чикен»</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Ролл темпурный «Окинава</t>
+          <t>Ролл темпурный «Окинава»</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Десерт «Бутерброд с колбасой</t>
+          <t>Десерт «Бутерброд с колбасой»</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Трайфл «Сникерс</t>
+          <t>Трайфл «Сникерс»</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Гренки из хлеба «Хоккайдо</t>
+          <t>Гренки из хлеба «Хоккайдо»</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Бульон «Том Ям</t>
+          <t>Бульон «Том Ям»</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Соус томатный «Маринара</t>
+          <t>Соус томатный «Маринара»</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Заправка «Греческая</t>
+          <t>Заправка «Греческая»</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Соус «Маяки</t>
+          <t>Соус «Маяки»</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Соус «Маяцу</t>
+          <t>Соус «Маяцу»</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Соус «Васабико</t>
+          <t>Соус «Васабико»</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Корж из печенья «Орео</t>
+          <t>Корж из печенья «Орео»</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
